--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1E50CE-28E5-45AA-BD56-2F82C887AC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66991ED0-7880-4B05-9E07-80AF8231E193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66991ED0-7880-4B05-9E07-80AF8231E193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F58B17C-3DD5-4BB7-A605-B812AAAB62C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F58B17C-3DD5-4BB7-A605-B812AAAB62C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F91F442-68C4-42BB-9212-9F9BF67E0D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
